--- a/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N51_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3616_W0026F0003T0006Z000C1N51_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.48632824067894</v>
+        <v>5.766528339110328</v>
       </c>
       <c r="D2" t="n">
-        <v>33.78623156767129</v>
+        <v>5.490262629746585</v>
       </c>
       <c r="E2" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F2" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.8851448988192</v>
+        <v>5.99383604605812</v>
       </c>
       <c r="D3" t="n">
-        <v>33.25479834979775</v>
+        <v>5.403904731842135</v>
       </c>
       <c r="E3" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F3" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>46.6815765038729</v>
+        <v>7.585756181879346</v>
       </c>
       <c r="D4" t="n">
-        <v>21.78302091079197</v>
+        <v>3.539740898003695</v>
       </c>
       <c r="E4" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F4" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>30.41715638311501</v>
+        <v>4.94278791225619</v>
       </c>
       <c r="D5" t="n">
-        <v>30.77308205916339</v>
+        <v>5.000625834614051</v>
       </c>
       <c r="E5" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F5" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>73.51580666393204</v>
+        <v>11.94631858288896</v>
       </c>
       <c r="D6" t="n">
-        <v>25.77792465922828</v>
+        <v>4.188912757124596</v>
       </c>
       <c r="E6" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F6" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>100.3466770548979</v>
+        <v>16.3063350214209</v>
       </c>
       <c r="D7" t="n">
-        <v>54.13538604901358</v>
+        <v>8.797000232964708</v>
       </c>
       <c r="E7" t="n">
-        <v>25.08050740211648</v>
+        <v>4.075582452843928</v>
       </c>
       <c r="F7" t="n">
-        <v>10.24650787156845</v>
+        <v>1.665057529129874</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
